--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/84.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/84.xlsx
@@ -426,13 +426,13 @@
         <v>-5.964659277067704</v>
       </c>
       <c r="E2">
-        <v>-11.47614694795197</v>
+        <v>-10.43268691015655</v>
       </c>
       <c r="F2">
-        <v>-1.73303835942059</v>
+        <v>-1.793434626758702</v>
       </c>
       <c r="G2">
-        <v>-8.554110686673695</v>
+        <v>-8.900486278153357</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.374357221743554</v>
       </c>
       <c r="E3">
-        <v>-12.17537956252833</v>
+        <v>-12.36082510161644</v>
       </c>
       <c r="F3">
-        <v>-1.609590078850991</v>
+        <v>-1.693548428594332</v>
       </c>
       <c r="G3">
-        <v>-8.282126950389763</v>
+        <v>-8.671411076202284</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.913161563267965</v>
       </c>
       <c r="E4">
-        <v>-13.41174353610249</v>
+        <v>-12.39196741736719</v>
       </c>
       <c r="F4">
-        <v>-1.459970358557344</v>
+        <v>-1.574420084030332</v>
       </c>
       <c r="G4">
-        <v>-9.005961145181708</v>
+        <v>-8.651238126054819</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.650833465156474</v>
       </c>
       <c r="E5">
-        <v>-13.0778229197249</v>
+        <v>-13.99404189485279</v>
       </c>
       <c r="F5">
-        <v>-1.560171336334778</v>
+        <v>-1.236772560444837</v>
       </c>
       <c r="G5">
-        <v>-8.006117155252394</v>
+        <v>-8.520940817929269</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.542416178408158</v>
       </c>
       <c r="E6">
-        <v>-13.72628228372726</v>
+        <v>-13.4477041481974</v>
       </c>
       <c r="F6">
-        <v>-1.376345012509928</v>
+        <v>-1.2607885881868</v>
       </c>
       <c r="G6">
-        <v>-8.498300389169101</v>
+        <v>-8.672579191077446</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.55981211085687</v>
       </c>
       <c r="E7">
-        <v>-15.05818800191525</v>
+        <v>-14.45323368770458</v>
       </c>
       <c r="F7">
-        <v>-1.046130429629753</v>
+        <v>-1.252116409846892</v>
       </c>
       <c r="G7">
-        <v>-8.64479052569051</v>
+        <v>-7.847109158481702</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.648423705675568</v>
       </c>
       <c r="E8">
-        <v>-15.18918316953513</v>
+        <v>-14.88292247239639</v>
       </c>
       <c r="F8">
-        <v>-0.8632327056634418</v>
+        <v>-0.7379471061944334</v>
       </c>
       <c r="G8">
-        <v>-8.97321127279689</v>
+        <v>-8.518591463292706</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.757499483662786</v>
       </c>
       <c r="E9">
-        <v>-16.67507964635395</v>
+        <v>-15.44696655242177</v>
       </c>
       <c r="F9">
-        <v>-0.6447292656225994</v>
+        <v>-0.7098646228721273</v>
       </c>
       <c r="G9">
-        <v>-8.242476669065434</v>
+        <v>-8.640511812776994</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.831133142180742</v>
       </c>
       <c r="E10">
-        <v>-16.47931371500236</v>
+        <v>-16.78821451248758</v>
       </c>
       <c r="F10">
-        <v>-0.76893550236576</v>
+        <v>-0.04629345955295813</v>
       </c>
       <c r="G10">
-        <v>-8.337441783438882</v>
+        <v>-8.898921135469504</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.816410394511976</v>
       </c>
       <c r="E11">
-        <v>-16.93672128909512</v>
+        <v>-18.53035921950444</v>
       </c>
       <c r="F11">
-        <v>0.04805178905408597</v>
+        <v>0.08716978291648703</v>
       </c>
       <c r="G11">
-        <v>-8.24628288607439</v>
+        <v>-7.733286863806124</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.671717643889983</v>
       </c>
       <c r="E12">
-        <v>-17.59760225730053</v>
+        <v>-16.86660692603436</v>
       </c>
       <c r="F12">
-        <v>0.136166886424675</v>
+        <v>-0.1398633562709819</v>
       </c>
       <c r="G12">
-        <v>-8.250361444472778</v>
+        <v>-8.138888504433764</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.363558462676862</v>
       </c>
       <c r="E13">
-        <v>-17.68252925884038</v>
+        <v>-17.94465091982636</v>
       </c>
       <c r="F13">
-        <v>0.3019637937275932</v>
+        <v>0.6814985434030483</v>
       </c>
       <c r="G13">
-        <v>-8.734942088036254</v>
+        <v>-6.807844572737218</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.888690670463496</v>
       </c>
       <c r="E14">
-        <v>-18.14999457370417</v>
+        <v>-18.50465107256289</v>
       </c>
       <c r="F14">
-        <v>0.8000859640530199</v>
+        <v>1.105140543807966</v>
       </c>
       <c r="G14">
-        <v>-7.723869757930518</v>
+        <v>-7.554722786541143</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.2602936474381</v>
       </c>
       <c r="E15">
-        <v>-19.00774189244503</v>
+        <v>-18.22414833557977</v>
       </c>
       <c r="F15">
-        <v>0.9063273969316678</v>
+        <v>1.344976101205701</v>
       </c>
       <c r="G15">
-        <v>-7.653884583289122</v>
+        <v>-7.633439291752222</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.515319450116249</v>
       </c>
       <c r="E16">
-        <v>-19.10051221096617</v>
+        <v>-19.76757001771803</v>
       </c>
       <c r="F16">
-        <v>1.469680186757944</v>
+        <v>1.514274517520253</v>
       </c>
       <c r="G16">
-        <v>-7.352802974216034</v>
+        <v>-8.55426490408699</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.703299608780163</v>
       </c>
       <c r="E17">
-        <v>-20.76202290980244</v>
+        <v>-20.4709959992255</v>
       </c>
       <c r="F17">
-        <v>1.853756046535546</v>
+        <v>1.774726482838862</v>
       </c>
       <c r="G17">
-        <v>-6.639786966905579</v>
+        <v>-6.696834284938084</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.8770841051254608</v>
       </c>
       <c r="E18">
-        <v>-21.2595165358111</v>
+        <v>-21.14334306361832</v>
       </c>
       <c r="F18">
-        <v>2.009770763178805</v>
+        <v>1.886499753233405</v>
       </c>
       <c r="G18">
-        <v>-5.991630866160667</v>
+        <v>-6.103034900546933</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.09373488371698752</v>
       </c>
       <c r="E19">
-        <v>-21.57781844533624</v>
+        <v>-22.43666165478696</v>
       </c>
       <c r="F19">
-        <v>2.483532304922704</v>
+        <v>2.359272224298361</v>
       </c>
       <c r="G19">
-        <v>-5.65408504189747</v>
+        <v>-5.213449798679639</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.6028439007028104</v>
       </c>
       <c r="E20">
-        <v>-22.89230312401672</v>
+        <v>-22.31810620526614</v>
       </c>
       <c r="F20">
-        <v>2.775664353193978</v>
+        <v>2.842962577732215</v>
       </c>
       <c r="G20">
-        <v>-4.564292925359096</v>
+        <v>-4.417763414178974</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.173348707871316</v>
       </c>
       <c r="E21">
-        <v>-23.51723706554924</v>
+        <v>-24.12793801327565</v>
       </c>
       <c r="F21">
-        <v>3.292945004811351</v>
+        <v>2.289266895087775</v>
       </c>
       <c r="G21">
-        <v>-4.170050873770254</v>
+        <v>-4.747857584280672</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.594774180891547</v>
       </c>
       <c r="E22">
-        <v>-23.84663373639318</v>
+        <v>-23.12101823224812</v>
       </c>
       <c r="F22">
-        <v>3.451635348165653</v>
+        <v>3.195509117424462</v>
       </c>
       <c r="G22">
-        <v>-3.742973638036049</v>
+        <v>-3.540059615578428</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.855224538176524</v>
       </c>
       <c r="E23">
-        <v>-25.35134602271387</v>
+        <v>-23.54794464779525</v>
       </c>
       <c r="F23">
-        <v>3.245226072205683</v>
+        <v>3.36215510131525</v>
       </c>
       <c r="G23">
-        <v>-3.493833766248971</v>
+        <v>-3.055928499368598</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.951974531400842</v>
       </c>
       <c r="E24">
-        <v>-25.14146936635438</v>
+        <v>-25.01728049516802</v>
       </c>
       <c r="F24">
-        <v>3.844293094236257</v>
+        <v>3.459461763387302</v>
       </c>
       <c r="G24">
-        <v>-2.844617830940358</v>
+        <v>-3.564442372986662</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.894714025386782</v>
       </c>
       <c r="E25">
-        <v>-25.72249975238253</v>
+        <v>-25.0433599769782</v>
       </c>
       <c r="F25">
-        <v>3.383278470086637</v>
+        <v>2.914528551129675</v>
       </c>
       <c r="G25">
-        <v>-3.232199002763528</v>
+        <v>-2.617360425733217</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.698926892531221</v>
       </c>
       <c r="E26">
-        <v>-25.97083221001516</v>
+        <v>-24.65227643320178</v>
       </c>
       <c r="F26">
-        <v>3.780816956894537</v>
+        <v>3.676543724964941</v>
       </c>
       <c r="G26">
-        <v>-2.717929866530198</v>
+        <v>-3.090532261934502</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.389787757644621</v>
       </c>
       <c r="E27">
-        <v>-26.95224309695747</v>
+        <v>-26.453676222609</v>
       </c>
       <c r="F27">
-        <v>3.134345781871358</v>
+        <v>2.809928942443376</v>
       </c>
       <c r="G27">
-        <v>-2.662946436858583</v>
+        <v>-3.721934445396889</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.9967129182811362</v>
       </c>
       <c r="E28">
-        <v>-26.66871986781124</v>
+        <v>-25.60370882221332</v>
       </c>
       <c r="F28">
-        <v>2.957361772793632</v>
+        <v>2.80193188353675</v>
       </c>
       <c r="G28">
-        <v>-2.564962598650445</v>
+        <v>-3.004643006394477</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.5503244022502771</v>
       </c>
       <c r="E29">
-        <v>-26.3034848536706</v>
+        <v>-26.93445525105535</v>
       </c>
       <c r="F29">
-        <v>3.309621697364511</v>
+        <v>2.995312596985489</v>
       </c>
       <c r="G29">
-        <v>-3.000771164954332</v>
+        <v>-4.166133095228277</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.08132582853716384</v>
       </c>
       <c r="E30">
-        <v>-26.07651773640617</v>
+        <v>-24.63631356232474</v>
       </c>
       <c r="F30">
-        <v>3.163610345477459</v>
+        <v>2.845969551404377</v>
       </c>
       <c r="G30">
-        <v>-2.970022837720776</v>
+        <v>-2.969980181840503</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.3825604217725552</v>
       </c>
       <c r="E31">
-        <v>-26.54781866875446</v>
+        <v>-24.76714117640634</v>
       </c>
       <c r="F31">
-        <v>3.181980221001941</v>
+        <v>2.63476734165181</v>
       </c>
       <c r="G31">
-        <v>-2.864187036320887</v>
+        <v>-3.36714908306037</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.8197673904699744</v>
       </c>
       <c r="E32">
-        <v>-26.44692879633757</v>
+        <v>-24.56200583233288</v>
       </c>
       <c r="F32">
-        <v>2.897556959781119</v>
+        <v>2.478363292329235</v>
       </c>
       <c r="G32">
-        <v>-4.072667499107494</v>
+        <v>-3.035181335448229</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.211079010918913</v>
       </c>
       <c r="E33">
-        <v>-25.99532219744864</v>
+        <v>-25.14303621836103</v>
       </c>
       <c r="F33">
-        <v>3.041363197641919</v>
+        <v>2.804377224109814</v>
       </c>
       <c r="G33">
-        <v>-3.480633411915325</v>
+        <v>-4.629553140954892</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.548134091696574</v>
       </c>
       <c r="E34">
-        <v>-25.35005993609569</v>
+        <v>-24.00898405804217</v>
       </c>
       <c r="F34">
-        <v>2.920867218495897</v>
+        <v>2.640645436742075</v>
       </c>
       <c r="G34">
-        <v>-3.745460803978108</v>
+        <v>-4.543017484767657</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.823679264312587</v>
       </c>
       <c r="E35">
-        <v>-25.74069968941935</v>
+        <v>-24.17568171473852</v>
       </c>
       <c r="F35">
-        <v>2.977464592924771</v>
+        <v>2.810215557564745</v>
       </c>
       <c r="G35">
-        <v>-3.781944706497574</v>
+        <v>-5.044614543338411</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.039745330439643</v>
       </c>
       <c r="E36">
-        <v>-25.21309171125969</v>
+        <v>-24.49835360168106</v>
       </c>
       <c r="F36">
-        <v>3.229783647082695</v>
+        <v>2.537054779552386</v>
       </c>
       <c r="G36">
-        <v>-3.975930525091945</v>
+        <v>-4.383041527636929</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.201892731029883</v>
       </c>
       <c r="E37">
-        <v>-24.68553807478812</v>
+        <v>-24.50325341055736</v>
       </c>
       <c r="F37">
-        <v>2.957418101777023</v>
+        <v>2.706041729723485</v>
       </c>
       <c r="G37">
-        <v>-4.313423849810191</v>
+        <v>-4.657998050653719</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.320035778988792</v>
       </c>
       <c r="E38">
-        <v>-24.61684565256576</v>
+        <v>-24.57829022486446</v>
       </c>
       <c r="F38">
-        <v>3.062072382711907</v>
+        <v>2.957832285478422</v>
       </c>
       <c r="G38">
-        <v>-4.259175413767892</v>
+        <v>-3.649232419304273</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.409686230292067</v>
       </c>
       <c r="E39">
-        <v>-24.06979240701716</v>
+        <v>-22.55790701786832</v>
       </c>
       <c r="F39">
-        <v>3.144277907030924</v>
+        <v>2.278776450298722</v>
       </c>
       <c r="G39">
-        <v>-4.866250620588556</v>
+        <v>-4.313151508420757</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.48330225482833</v>
       </c>
       <c r="E40">
-        <v>-23.69931794844965</v>
+        <v>-21.84855326388481</v>
       </c>
       <c r="F40">
-        <v>3.099025852550793</v>
+        <v>2.711888346852444</v>
       </c>
       <c r="G40">
-        <v>-4.072677342772173</v>
+        <v>-4.512695716336828</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.558054283267511</v>
       </c>
       <c r="E41">
-        <v>-23.5937275200128</v>
+        <v>-22.19473245940117</v>
       </c>
       <c r="F41">
-        <v>3.250544190931656</v>
+        <v>2.939604889147222</v>
       </c>
       <c r="G41">
-        <v>-4.550515076030988</v>
+        <v>-4.370192264010144</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.643425068533285</v>
       </c>
       <c r="E42">
-        <v>-22.5362835544817</v>
+        <v>-22.29069082362371</v>
       </c>
       <c r="F42">
-        <v>3.256636004811843</v>
+        <v>3.077387239254864</v>
       </c>
       <c r="G42">
-        <v>-4.219108417305512</v>
+        <v>-3.960095349846065</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.748803635149906</v>
       </c>
       <c r="E43">
-        <v>-22.58506427649232</v>
+        <v>-22.12244895729074</v>
       </c>
       <c r="F43">
-        <v>3.010216583296658</v>
+        <v>2.326753833534064</v>
       </c>
       <c r="G43">
-        <v>-4.145067652816642</v>
+        <v>-4.957865607749811</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.875676504803487</v>
       </c>
       <c r="E44">
-        <v>-22.87614100028335</v>
+        <v>-21.50820674289033</v>
       </c>
       <c r="F44">
-        <v>2.864074349359963</v>
+        <v>2.798586935964245</v>
       </c>
       <c r="G44">
-        <v>-3.895176381292452</v>
+        <v>-4.160098928780458</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.021668031280246</v>
       </c>
       <c r="E45">
-        <v>-21.9220503970293</v>
+        <v>-20.05043208965915</v>
       </c>
       <c r="F45">
-        <v>3.152462176970583</v>
+        <v>2.368313026132515</v>
       </c>
       <c r="G45">
-        <v>-3.997005811168258</v>
+        <v>-4.079482596286461</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.17938337300093</v>
       </c>
       <c r="E46">
-        <v>-22.3252838365683</v>
+        <v>-19.64856172079645</v>
       </c>
       <c r="F46">
-        <v>2.91772273583487</v>
+        <v>2.337872180814439</v>
       </c>
       <c r="G46">
-        <v>-3.967268100175011</v>
+        <v>-4.283761606912811</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.33680792318235</v>
       </c>
       <c r="E47">
-        <v>-21.44624363304338</v>
+        <v>-19.53119273146566</v>
       </c>
       <c r="F47">
-        <v>3.116791019871231</v>
+        <v>2.391416192996593</v>
       </c>
       <c r="G47">
-        <v>-3.915897295440345</v>
+        <v>-3.90061992785957</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.483632967574202</v>
       </c>
       <c r="E48">
-        <v>-20.67767555293558</v>
+        <v>-20.27302470103217</v>
       </c>
       <c r="F48">
-        <v>3.002110179892862</v>
+        <v>2.593181641296469</v>
       </c>
       <c r="G48">
-        <v>-3.968629807122181</v>
+        <v>-2.981959921754036</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.607184673183138</v>
       </c>
       <c r="E49">
-        <v>-20.71321048847376</v>
+        <v>-19.37261010019105</v>
       </c>
       <c r="F49">
-        <v>2.952524107161283</v>
+        <v>2.713907906580469</v>
       </c>
       <c r="G49">
-        <v>-3.606816068205331</v>
+        <v>-3.678566540045709</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.701546134531022</v>
       </c>
       <c r="E50">
-        <v>-19.97893654202604</v>
+        <v>-17.51417418065721</v>
       </c>
       <c r="F50">
-        <v>2.627929997109103</v>
+        <v>2.931917639649243</v>
       </c>
       <c r="G50">
-        <v>-4.055421398591053</v>
+        <v>-4.319083957000233</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.763053015985574</v>
       </c>
       <c r="E51">
-        <v>-19.99403447436762</v>
+        <v>-18.46263136224572</v>
       </c>
       <c r="F51">
-        <v>2.651212091332185</v>
+        <v>2.56610728110337</v>
       </c>
       <c r="G51">
-        <v>-3.696052169735989</v>
+        <v>-4.217900927771637</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.795804469275337</v>
       </c>
       <c r="E52">
-        <v>-18.78506776853986</v>
+        <v>-17.49668521403959</v>
       </c>
       <c r="F52">
-        <v>2.857043166845001</v>
+        <v>2.320302508201062</v>
       </c>
       <c r="G52">
-        <v>-3.708665185410495</v>
+        <v>-4.150156827455341</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.808836481514714</v>
       </c>
       <c r="E53">
-        <v>-18.86672974032018</v>
+        <v>-17.32124307403443</v>
       </c>
       <c r="F53">
-        <v>2.78751000705401</v>
+        <v>2.793585253586142</v>
       </c>
       <c r="G53">
-        <v>-3.687980364699755</v>
+        <v>-4.562973874292199</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.813394307291905</v>
       </c>
       <c r="E54">
-        <v>-18.76066382211253</v>
+        <v>-16.99541484070854</v>
       </c>
       <c r="F54">
-        <v>2.771664995373261</v>
+        <v>2.332004026133007</v>
       </c>
       <c r="G54">
-        <v>-3.746222047379899</v>
+        <v>-2.513595075137338</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.824660880398565</v>
       </c>
       <c r="E55">
-        <v>-17.81695248128406</v>
+        <v>-16.80786808968087</v>
       </c>
       <c r="F55">
-        <v>2.652100101187987</v>
+        <v>1.997456253368788</v>
       </c>
       <c r="G55">
-        <v>-3.418270514956518</v>
+        <v>-4.345031857092322</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.852299005403014</v>
       </c>
       <c r="E56">
-        <v>-18.09786278092787</v>
+        <v>-16.23084993162351</v>
       </c>
       <c r="F56">
-        <v>2.795760546385894</v>
+        <v>2.203897007290064</v>
       </c>
       <c r="G56">
-        <v>-3.55239700864194</v>
+        <v>-3.071645550638338</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.905907478488402</v>
       </c>
       <c r="E57">
-        <v>-17.38816033444577</v>
+        <v>-17.22878522021982</v>
       </c>
       <c r="F57">
-        <v>2.542121074587907</v>
+        <v>2.221582651339833</v>
       </c>
       <c r="G57">
-        <v>-4.068460973068286</v>
+        <v>-3.393589166386375</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.986448189014762</v>
       </c>
       <c r="E58">
-        <v>-17.23589492441187</v>
+        <v>-16.52736082422375</v>
       </c>
       <c r="F58">
-        <v>2.807640991676844</v>
+        <v>2.38113284005824</v>
       </c>
       <c r="G58">
-        <v>-3.692160640966488</v>
+        <v>-4.518116294353031</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.091354493654481</v>
       </c>
       <c r="E59">
-        <v>-16.07132990622932</v>
+        <v>-15.9309834397836</v>
       </c>
       <c r="F59">
-        <v>2.247959526179775</v>
+        <v>2.196297564736781</v>
       </c>
       <c r="G59">
-        <v>-4.339037065303216</v>
+        <v>-3.911526708323164</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.212112240955998</v>
       </c>
       <c r="E60">
-        <v>-17.08008371922995</v>
+        <v>-15.15349879435469</v>
       </c>
       <c r="F60">
-        <v>2.527197207459071</v>
+        <v>2.190358170458709</v>
       </c>
       <c r="G60">
-        <v>-4.12416299026142</v>
+        <v>-3.788247933113267</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.337330605596949</v>
       </c>
       <c r="E61">
-        <v>-16.25528104889489</v>
+        <v>-15.64354308062073</v>
       </c>
       <c r="F61">
-        <v>2.659301927387926</v>
+        <v>2.065889341248861</v>
       </c>
       <c r="G61">
-        <v>-4.65001155737803</v>
+        <v>-4.78136870006728</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.456272889813325</v>
       </c>
       <c r="E62">
-        <v>-16.22784302488242</v>
+        <v>-16.16313113131281</v>
       </c>
       <c r="F62">
-        <v>2.303604278095429</v>
+        <v>2.489332533477106</v>
       </c>
       <c r="G62">
-        <v>-4.374339728061282</v>
+        <v>-4.561343107177155</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.555628009821157</v>
       </c>
       <c r="E63">
-        <v>-15.93076154455722</v>
+        <v>-15.47155163780941</v>
       </c>
       <c r="F63">
-        <v>2.152372554835934</v>
+        <v>2.076578594214585</v>
       </c>
       <c r="G63">
-        <v>-4.965077732737471</v>
+        <v>-4.245016942738888</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.627571135203655</v>
       </c>
       <c r="E64">
-        <v>-15.50037990334224</v>
+        <v>-15.69326119675094</v>
       </c>
       <c r="F64">
-        <v>2.48316119632625</v>
+        <v>1.938219700394595</v>
       </c>
       <c r="G64">
-        <v>-4.561802478195478</v>
+        <v>-4.776361555967568</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.663982595364701</v>
       </c>
       <c r="E65">
-        <v>-15.52176335760646</v>
+        <v>-16.00484737932271</v>
       </c>
       <c r="F65">
-        <v>2.022885475899927</v>
+        <v>2.310332278140967</v>
       </c>
       <c r="G65">
-        <v>-4.931035059058232</v>
+        <v>-5.596794913469565</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.662747211559648</v>
       </c>
       <c r="E66">
-        <v>-14.99814949352156</v>
+        <v>-15.93101966757566</v>
       </c>
       <c r="F66">
-        <v>2.67928214914345</v>
+        <v>1.656998907552997</v>
       </c>
       <c r="G66">
-        <v>-5.284071530303567</v>
+        <v>-5.191629675309331</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.623601343743047</v>
       </c>
       <c r="E67">
-        <v>-15.49076142454995</v>
+        <v>-14.30197812737438</v>
       </c>
       <c r="F67">
-        <v>2.123876716179632</v>
+        <v>1.732491342439727</v>
       </c>
       <c r="G67">
-        <v>-5.145121640925762</v>
+        <v>-6.079613541055617</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.550422429899575</v>
       </c>
       <c r="E68">
-        <v>-14.86804643528119</v>
+        <v>-16.12660898844095</v>
       </c>
       <c r="F68">
-        <v>1.938516255924797</v>
+        <v>1.688316165583235</v>
       </c>
       <c r="G68">
-        <v>-5.756669152731949</v>
+        <v>-5.930294991549967</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.450440833464996</v>
       </c>
       <c r="E69">
-        <v>-16.38691473134986</v>
+        <v>-15.42391661972272</v>
       </c>
       <c r="F69">
-        <v>2.088298336229393</v>
+        <v>1.807871119359676</v>
       </c>
       <c r="G69">
-        <v>-4.918376106281895</v>
+        <v>-6.594591421145787</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.330242747197779</v>
       </c>
       <c r="E70">
-        <v>-15.67513824377225</v>
+        <v>-15.0042538764839</v>
       </c>
       <c r="F70">
-        <v>2.210048463623253</v>
+        <v>1.068407419698225</v>
       </c>
       <c r="G70">
-        <v>-5.119324677025408</v>
+        <v>-6.539358618635654</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.200001115263276</v>
       </c>
       <c r="E71">
-        <v>-16.12759166730061</v>
+        <v>-14.78123106008014</v>
       </c>
       <c r="F71">
-        <v>2.010189917084622</v>
+        <v>1.562805250180665</v>
       </c>
       <c r="G71">
-        <v>-5.841849664415134</v>
+        <v>-6.170939780719642</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.066182433334297</v>
       </c>
       <c r="E72">
-        <v>-15.41082027289254</v>
+        <v>-15.04366065729864</v>
       </c>
       <c r="F72">
-        <v>2.008549749627079</v>
+        <v>1.599241818760204</v>
       </c>
       <c r="G72">
-        <v>-5.687140067887316</v>
+        <v>-5.682589013584366</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.937391306330436</v>
       </c>
       <c r="E73">
-        <v>-15.66765267623757</v>
+        <v>-15.05515392433011</v>
       </c>
       <c r="F73">
-        <v>1.859996966548238</v>
+        <v>1.852380956646899</v>
       </c>
       <c r="G73">
-        <v>-5.72848017831476</v>
+        <v>-5.999413923699669</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.817935827483687</v>
       </c>
       <c r="E74">
-        <v>-15.932400852148</v>
+        <v>-15.37905755620274</v>
       </c>
       <c r="F74">
-        <v>1.830220471887207</v>
+        <v>1.693443759806563</v>
       </c>
       <c r="G74">
-        <v>-5.226640309348607</v>
+        <v>-5.201909742455071</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.711676422556899</v>
       </c>
       <c r="E75">
-        <v>-15.87449978348593</v>
+        <v>-16.86520762756599</v>
       </c>
       <c r="F75">
-        <v>2.043175507064098</v>
+        <v>1.664631484802391</v>
       </c>
       <c r="G75">
-        <v>-4.835633542217377</v>
+        <v>-4.994881068161908</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.62024064920838</v>
       </c>
       <c r="E76">
-        <v>-15.81557527969812</v>
+        <v>-16.71442302853259</v>
       </c>
       <c r="F76">
-        <v>1.597691114982163</v>
+        <v>1.027772685121298</v>
       </c>
       <c r="G76">
-        <v>-4.777283579225772</v>
+        <v>-6.067387709525126</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.540964554552524</v>
       </c>
       <c r="E77">
-        <v>-16.78634425272241</v>
+        <v>-17.84562677870063</v>
       </c>
       <c r="F77">
-        <v>1.895870245293873</v>
+        <v>1.091686200451696</v>
       </c>
       <c r="G77">
-        <v>-5.046117342812637</v>
+        <v>-6.378811728953584</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.472143243876866</v>
       </c>
       <c r="E78">
-        <v>-16.15475798287263</v>
+        <v>-16.91717186680401</v>
       </c>
       <c r="F78">
-        <v>1.402007540153642</v>
+        <v>1.337416420287753</v>
       </c>
       <c r="G78">
-        <v>-4.420572139833858</v>
+        <v>-4.881793767115645</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.406899612042702</v>
       </c>
       <c r="E79">
-        <v>-16.78708692245967</v>
+        <v>-16.50370407600768</v>
       </c>
       <c r="F79">
-        <v>1.570919937258489</v>
+        <v>1.13383187717133</v>
       </c>
       <c r="G79">
-        <v>-4.560857486386357</v>
+        <v>-6.188221974673237</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.341368284628871</v>
       </c>
       <c r="E80">
-        <v>-18.18883529526796</v>
+        <v>-17.87495317637431</v>
       </c>
       <c r="F80">
-        <v>1.723091029152758</v>
+        <v>0.9033767522428959</v>
       </c>
       <c r="G80">
-        <v>-4.527090435318112</v>
+        <v>-5.09685815300789</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.268721326130864</v>
       </c>
       <c r="E81">
-        <v>-17.99145722716964</v>
+        <v>-18.92738412117892</v>
       </c>
       <c r="F81">
-        <v>1.63922545655853</v>
+        <v>1.05987523544939</v>
       </c>
       <c r="G81">
-        <v>-4.103392857790134</v>
+        <v>-5.305931028332588</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.185121864122792</v>
       </c>
       <c r="E82">
-        <v>-19.02960083648005</v>
+        <v>-17.55911928518334</v>
       </c>
       <c r="F82">
-        <v>1.641955755518157</v>
+        <v>0.9261899905159943</v>
       </c>
       <c r="G82">
-        <v>-3.673372366317107</v>
+        <v>-4.795231861155934</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.088233808139064</v>
       </c>
       <c r="E83">
-        <v>-18.86247750322698</v>
+        <v>-19.27779291141844</v>
       </c>
       <c r="F83">
-        <v>1.303592522496643</v>
+        <v>0.9254378329142523</v>
       </c>
       <c r="G83">
-        <v>-4.039143258434648</v>
+        <v>-4.060172607409129</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.975715032588549</v>
       </c>
       <c r="E84">
-        <v>-20.31815547299262</v>
+        <v>-20.11165252976884</v>
       </c>
       <c r="F84">
-        <v>1.745150453089309</v>
+        <v>1.379598545173109</v>
       </c>
       <c r="G84">
-        <v>-3.70982017539942</v>
+        <v>-4.023347457847481</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.849338052554028</v>
       </c>
       <c r="E85">
-        <v>-21.73213072562162</v>
+        <v>-21.28181474182487</v>
       </c>
       <c r="F85">
-        <v>1.591933961532707</v>
+        <v>1.495951030570328</v>
       </c>
       <c r="G85">
-        <v>-3.182678806988388</v>
+        <v>-4.584200096560247</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.710089935509274</v>
       </c>
       <c r="E86">
-        <v>-21.955524876894</v>
+        <v>-23.00739429092167</v>
       </c>
       <c r="F86">
-        <v>1.909168855578416</v>
+        <v>0.899037763787032</v>
       </c>
       <c r="G86">
-        <v>-3.128643650347453</v>
+        <v>-4.473403088162478</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.564483594911088</v>
       </c>
       <c r="E87">
-        <v>-23.37978882246843</v>
+        <v>-23.85192299403413</v>
       </c>
       <c r="F87">
-        <v>1.729078468740193</v>
+        <v>1.420332683838372</v>
       </c>
       <c r="G87">
-        <v>-2.846091099420549</v>
+        <v>-3.465014797292368</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.420850737265224</v>
       </c>
       <c r="E88">
-        <v>-23.95924782801592</v>
+        <v>-25.44573753492975</v>
       </c>
       <c r="F88">
-        <v>1.62594838382646</v>
+        <v>1.510157531528339</v>
       </c>
       <c r="G88">
-        <v>-3.398773496450298</v>
+        <v>-3.510233311603076</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.289525922039275</v>
       </c>
       <c r="E89">
-        <v>-26.16365916173577</v>
+        <v>-26.28005452915492</v>
       </c>
       <c r="F89">
-        <v>1.375372214684026</v>
+        <v>1.2883704431028</v>
       </c>
       <c r="G89">
-        <v>-2.59678388533394</v>
+        <v>-4.149549801466843</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.182765372871732</v>
       </c>
       <c r="E90">
-        <v>-26.66319965799589</v>
+        <v>-26.71506879927975</v>
       </c>
       <c r="F90">
-        <v>2.079050442544539</v>
+        <v>1.566938803520634</v>
       </c>
       <c r="G90">
-        <v>-2.891608204893166</v>
+        <v>-3.167467063838802</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.109557829751914</v>
       </c>
       <c r="E91">
-        <v>-29.05226857632651</v>
+        <v>-28.85100507752961</v>
       </c>
       <c r="F91">
-        <v>1.655499562553929</v>
+        <v>1.043871177227303</v>
       </c>
       <c r="G91">
-        <v>-2.339867518450978</v>
+        <v>-4.544379191714826</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.078704085063003</v>
       </c>
       <c r="E92">
-        <v>-30.61589178101299</v>
+        <v>-29.34480346874801</v>
       </c>
       <c r="F92">
-        <v>1.529350804251204</v>
+        <v>1.322323566208746</v>
       </c>
       <c r="G92">
-        <v>-2.915239562564287</v>
+        <v>-3.391115125330554</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.094836347353573</v>
       </c>
       <c r="E93">
-        <v>-31.93206784473533</v>
+        <v>-31.50902912412379</v>
       </c>
       <c r="F93">
-        <v>1.674379712398536</v>
+        <v>1.130274867543708</v>
       </c>
       <c r="G93">
-        <v>-2.852965258587586</v>
+        <v>-4.0384837329012</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.160473481541632</v>
       </c>
       <c r="E94">
-        <v>-33.96173895192121</v>
+        <v>-33.60156450748413</v>
       </c>
       <c r="F94">
-        <v>1.599765346958773</v>
+        <v>0.9184315014213741</v>
       </c>
       <c r="G94">
-        <v>-2.546564789366638</v>
+        <v>-3.429475886582023</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.275594554654147</v>
       </c>
       <c r="E95">
-        <v>-35.93966997933244</v>
+        <v>-37.19942352115621</v>
       </c>
       <c r="F95">
-        <v>1.596002902215258</v>
+        <v>0.6378179018860276</v>
       </c>
       <c r="G95">
-        <v>-2.933004096087121</v>
+        <v>-4.784594140860214</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.437105321306519</v>
       </c>
       <c r="E96">
-        <v>-38.13031248783196</v>
+        <v>-38.4120084777161</v>
       </c>
       <c r="F96">
-        <v>1.234556383147333</v>
+        <v>0.8687360841926262</v>
       </c>
       <c r="G96">
-        <v>-2.717408152302246</v>
+        <v>-4.294799636238783</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.635884575452933</v>
       </c>
       <c r="E97">
-        <v>-40.41231922367324</v>
+        <v>-39.74452780413213</v>
       </c>
       <c r="F97">
-        <v>1.43905047367203</v>
+        <v>0.571115273510403</v>
       </c>
       <c r="G97">
-        <v>-2.883388744886757</v>
+        <v>-4.912538813127642</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.868729015801816</v>
       </c>
       <c r="E98">
-        <v>-43.12122293998059</v>
+        <v>-42.53953366098433</v>
       </c>
       <c r="F98">
-        <v>1.279604659246375</v>
+        <v>1.016977401128015</v>
       </c>
       <c r="G98">
-        <v>-3.613385073767339</v>
+        <v>-4.401340900273953</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.116698117526846</v>
       </c>
       <c r="E99">
-        <v>-44.69393026352645</v>
+        <v>-46.10705416304202</v>
       </c>
       <c r="F99">
-        <v>1.103967575565602</v>
+        <v>0.03870531964829915</v>
       </c>
       <c r="G99">
-        <v>-3.934964473922278</v>
+        <v>-4.752041141768963</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.387444999132803</v>
       </c>
       <c r="E100">
-        <v>-47.21357772986825</v>
+        <v>-47.08686876289663</v>
       </c>
       <c r="F100">
-        <v>0.891555949404947</v>
+        <v>-0.004538772247446243</v>
       </c>
       <c r="G100">
-        <v>-4.048927861124912</v>
+        <v>-4.490353878738569</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.646565142206873</v>
       </c>
       <c r="E101">
-        <v>-50.0197134437128</v>
+        <v>-50.11158146378791</v>
       </c>
       <c r="F101">
-        <v>0.9274954975428062</v>
+        <v>-0.02770406666673442</v>
       </c>
       <c r="G101">
-        <v>-4.343355152875445</v>
+        <v>-5.434814129966017</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.936212411426878</v>
       </c>
       <c r="E102">
-        <v>-53.22934411647029</v>
+        <v>-53.15080565963677</v>
       </c>
       <c r="F102">
-        <v>0.5104514435011868</v>
+        <v>-0.8105303147625316</v>
       </c>
       <c r="G102">
-        <v>-5.091499918201317</v>
+        <v>-5.0880546355639</v>
       </c>
     </row>
   </sheetData>
